--- a/python/Jupyter_project/ga4entity_check/data/0702/all_book_check_0702.xlsx
+++ b/python/Jupyter_project/ga4entity_check/data/0702/all_book_check_0702.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hj7724\VScode\python\Jupyter_project\ga4entity_check\data\0702\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A23C0E3-CFDD-4907-82F7-026898C02F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625E48B2-BC85-4393-B6F6-17D44CCC0BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
